--- a/produkty.xlsx
+++ b/produkty.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produkty" sheetId="1" r:id="Rb16c3b927a184b13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrukcja" sheetId="2" r:id="Rbcf2a23f5f3c4529"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produkty" sheetId="1" r:id="Re2a1cd12cfb04983"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrukcja" sheetId="2" r:id="Re4b87fb54c194573"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5622,7 +5622,7 @@
         <x:v>zdjecia-produktow/torby/Mała Mi.webp</x:v>
       </x:c>
       <x:c r="E327" t="str">
-        <x:v>tak</x:v>
+        <x:v>nie</x:v>
       </x:c>
       <x:c r="F327"/>
     </x:row>
@@ -5638,7 +5638,7 @@
         <x:v>zdjecia-produktow/torby/Włoczykij ver 2.webp</x:v>
       </x:c>
       <x:c r="E328" t="str">
-        <x:v>tak</x:v>
+        <x:v>nie</x:v>
       </x:c>
       <x:c r="F328"/>
     </x:row>
@@ -5654,7 +5654,7 @@
         <x:v>zdjecia-produktow/torby/Włoczykij.webp</x:v>
       </x:c>
       <x:c r="E329" t="str">
-        <x:v>tak</x:v>
+        <x:v>nie</x:v>
       </x:c>
       <x:c r="F329"/>
     </x:row>
@@ -5677,7 +5677,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c26d415e0224e53"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R521f9f714bc04261"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/produkty.xlsx
+++ b/produkty.xlsx
@@ -2,66 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produkty" sheetId="1" r:id="Re2a1cd12cfb04983"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrukcja" sheetId="2" r:id="Re4b87fb54c194573"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produkty" sheetId="1" r:id="R731c252bfb4f4657"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrukcja" sheetId="2" r:id="Re9c926ac425c4b9d"/>
   </x:sheets>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:si>
-    <x:t xml:space="preserve">kategoria</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">seria</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">tytuł</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">zdjęcie</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">aktywne</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">notatka</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Jak aktualizować produkty</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Box, Breloki, Frotki, Kosmetyczka, Torby albo Workoplecak.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Wpisuj tylko dla kategorii Torby. Pozostałe kategorie zostaw puste.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Podpis pod zdjęciem. Może być pusty, wtedy strona zrobi podpis z nazwy pliku.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Ścieżka do pliku, np. zdjecia-produktow/workoplecaki/111.png.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">tak = pokazuj produkt, nie = ukryj produkt.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Pole tylko dla Ciebie, strona go nie używa.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Po zmianach</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Zapisz arkusz jako produkty.csv i uruchom aktualizuj-produkty.bat.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Publikacja</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">W GitHub Desktop zrób Commit, potem Push origin.</x:t>
-  </x:si>
-</x:sst>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -295,23 +243,23 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="1" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B1" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C1" s="1" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D1" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E1" s="1" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F1" s="1" t="s">
-        <x:v>5</x:v>
+      <x:c r="A1" s="1" t="str">
+        <x:v>kategoria</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="str">
+        <x:v>seria</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="str">
+        <x:v>tytuł</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="str">
+        <x:v>zdjęcie</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="str">
+        <x:v>aktywne</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="str">
+        <x:v>notatka</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -371,7 +319,7 @@
       </x:c>
       <x:c r="C5"/>
       <x:c r="D5" t="str">
-        <x:v>zdjecia-produktow/torby/Afrykański styl/SA_01.png</x:v>
+        <x:v>zdjecia-produktow/torby/Afrykański styl/SA_01.webp</x:v>
       </x:c>
       <x:c r="E5" t="str">
         <x:v>tak</x:v>
@@ -387,7 +335,7 @@
       </x:c>
       <x:c r="C6"/>
       <x:c r="D6" t="str">
-        <x:v>zdjecia-produktow/torby/Afrykański styl/SA_02.png</x:v>
+        <x:v>zdjecia-produktow/torby/Afrykański styl/SA_02.webp</x:v>
       </x:c>
       <x:c r="E6" t="str">
         <x:v>tak</x:v>
@@ -403,7 +351,7 @@
       </x:c>
       <x:c r="C7"/>
       <x:c r="D7" t="str">
-        <x:v>zdjecia-produktow/torby/Afrykański styl/SA_03.png</x:v>
+        <x:v>zdjecia-produktow/torby/Afrykański styl/SA_03.webp</x:v>
       </x:c>
       <x:c r="E7" t="str">
         <x:v>tak</x:v>
@@ -419,7 +367,7 @@
       </x:c>
       <x:c r="C8"/>
       <x:c r="D8" t="str">
-        <x:v>zdjecia-produktow/torby/Afrykański styl/SA_04.png</x:v>
+        <x:v>zdjecia-produktow/torby/Afrykański styl/SA_04.webp</x:v>
       </x:c>
       <x:c r="E8" t="str">
         <x:v>tak</x:v>
@@ -435,7 +383,7 @@
       </x:c>
       <x:c r="C9"/>
       <x:c r="D9" t="str">
-        <x:v>zdjecia-produktow/torby/Afrykański styl/SA_05.png</x:v>
+        <x:v>zdjecia-produktow/torby/Afrykański styl/SA_05.webp</x:v>
       </x:c>
       <x:c r="E9" t="str">
         <x:v>tak</x:v>
@@ -451,7 +399,7 @@
       </x:c>
       <x:c r="C10"/>
       <x:c r="D10" t="str">
-        <x:v>zdjecia-produktow/torby/Afrykański styl/SA_06.png</x:v>
+        <x:v>zdjecia-produktow/torby/Afrykański styl/SA_06.webp</x:v>
       </x:c>
       <x:c r="E10" t="str">
         <x:v>tak</x:v>
@@ -467,7 +415,7 @@
       </x:c>
       <x:c r="C11"/>
       <x:c r="D11" t="str">
-        <x:v>zdjecia-produktow/torby/Afrykański styl/SA_07.png</x:v>
+        <x:v>zdjecia-produktow/torby/Afrykański styl/SA_07.webp</x:v>
       </x:c>
       <x:c r="E11" t="str">
         <x:v>tak</x:v>
@@ -483,7 +431,7 @@
       </x:c>
       <x:c r="C12"/>
       <x:c r="D12" t="str">
-        <x:v>zdjecia-produktow/torby/Afrykański styl/SA_08.png</x:v>
+        <x:v>zdjecia-produktow/torby/Afrykański styl/SA_08.webp</x:v>
       </x:c>
       <x:c r="E12" t="str">
         <x:v>tak</x:v>
@@ -499,7 +447,7 @@
       </x:c>
       <x:c r="C13"/>
       <x:c r="D13" t="str">
-        <x:v>zdjecia-produktow/torby/Afrykański styl/SA_09.png</x:v>
+        <x:v>zdjecia-produktow/torby/Afrykański styl/SA_09.webp</x:v>
       </x:c>
       <x:c r="E13" t="str">
         <x:v>tak</x:v>
@@ -515,7 +463,7 @@
       </x:c>
       <x:c r="C14"/>
       <x:c r="D14" t="str">
-        <x:v>zdjecia-produktow/torby/Afrykański styl/SA_10.png</x:v>
+        <x:v>zdjecia-produktow/torby/Afrykański styl/SA_10.webp</x:v>
       </x:c>
       <x:c r="E14" t="str">
         <x:v>tak</x:v>
@@ -531,7 +479,7 @@
       </x:c>
       <x:c r="C15"/>
       <x:c r="D15" t="str">
-        <x:v>zdjecia-produktow/torby/Afrykański styl/SA_11.png</x:v>
+        <x:v>zdjecia-produktow/torby/Afrykański styl/SA_11.webp</x:v>
       </x:c>
       <x:c r="E15" t="str">
         <x:v>tak</x:v>
@@ -547,7 +495,7 @@
       </x:c>
       <x:c r="C16"/>
       <x:c r="D16" t="str">
-        <x:v>zdjecia-produktow/torby/Afrykański styl/SA_12.png</x:v>
+        <x:v>zdjecia-produktow/torby/Afrykański styl/SA_12.webp</x:v>
       </x:c>
       <x:c r="E16" t="str">
         <x:v>tak</x:v>
@@ -563,7 +511,7 @@
       </x:c>
       <x:c r="C17"/>
       <x:c r="D17" t="str">
-        <x:v>zdjecia-produktow/torby/Anioły Bieszczadzkie/ANI_01.png</x:v>
+        <x:v>zdjecia-produktow/torby/Anioły Bieszczadzkie/ANI_01.webp</x:v>
       </x:c>
       <x:c r="E17" t="str">
         <x:v>tak</x:v>
@@ -579,7 +527,7 @@
       </x:c>
       <x:c r="C18"/>
       <x:c r="D18" t="str">
-        <x:v>zdjecia-produktow/torby/Anioły Bieszczadzkie/ANI_02.png</x:v>
+        <x:v>zdjecia-produktow/torby/Anioły Bieszczadzkie/ANI_02.webp</x:v>
       </x:c>
       <x:c r="E18" t="str">
         <x:v>tak</x:v>
@@ -595,7 +543,7 @@
       </x:c>
       <x:c r="C19"/>
       <x:c r="D19" t="str">
-        <x:v>zdjecia-produktow/torby/Anioły Bieszczadzkie/ANI_03.png</x:v>
+        <x:v>zdjecia-produktow/torby/Anioły Bieszczadzkie/ANI_03.webp</x:v>
       </x:c>
       <x:c r="E19" t="str">
         <x:v>tak</x:v>
@@ -611,7 +559,7 @@
       </x:c>
       <x:c r="C20"/>
       <x:c r="D20" t="str">
-        <x:v>zdjecia-produktow/torby/Anioły Bieszczadzkie/ANI_04.png</x:v>
+        <x:v>zdjecia-produktow/torby/Anioły Bieszczadzkie/ANI_04.webp</x:v>
       </x:c>
       <x:c r="E20" t="str">
         <x:v>tak</x:v>
@@ -627,7 +575,7 @@
       </x:c>
       <x:c r="C21"/>
       <x:c r="D21" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_01.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_01.webp</x:v>
       </x:c>
       <x:c r="E21" t="str">
         <x:v>tak</x:v>
@@ -643,7 +591,7 @@
       </x:c>
       <x:c r="C22"/>
       <x:c r="D22" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_02.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_02.webp</x:v>
       </x:c>
       <x:c r="E22" t="str">
         <x:v>tak</x:v>
@@ -659,7 +607,7 @@
       </x:c>
       <x:c r="C23"/>
       <x:c r="D23" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_03.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_03.webp</x:v>
       </x:c>
       <x:c r="E23" t="str">
         <x:v>tak</x:v>
@@ -675,7 +623,7 @@
       </x:c>
       <x:c r="C24"/>
       <x:c r="D24" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_04.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_04.webp</x:v>
       </x:c>
       <x:c r="E24" t="str">
         <x:v>tak</x:v>
@@ -691,7 +639,7 @@
       </x:c>
       <x:c r="C25"/>
       <x:c r="D25" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_05.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_05.webp</x:v>
       </x:c>
       <x:c r="E25" t="str">
         <x:v>tak</x:v>
@@ -707,7 +655,7 @@
       </x:c>
       <x:c r="C26"/>
       <x:c r="D26" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_06.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_06.webp</x:v>
       </x:c>
       <x:c r="E26" t="str">
         <x:v>tak</x:v>
@@ -723,7 +671,7 @@
       </x:c>
       <x:c r="C27"/>
       <x:c r="D27" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_07.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_07.webp</x:v>
       </x:c>
       <x:c r="E27" t="str">
         <x:v>tak</x:v>
@@ -739,7 +687,7 @@
       </x:c>
       <x:c r="C28"/>
       <x:c r="D28" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_08.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_08.webp</x:v>
       </x:c>
       <x:c r="E28" t="str">
         <x:v>tak</x:v>
@@ -755,7 +703,7 @@
       </x:c>
       <x:c r="C29"/>
       <x:c r="D29" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_09.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_09.webp</x:v>
       </x:c>
       <x:c r="E29" t="str">
         <x:v>tak</x:v>
@@ -771,7 +719,7 @@
       </x:c>
       <x:c r="C30"/>
       <x:c r="D30" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_10.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_10.webp</x:v>
       </x:c>
       <x:c r="E30" t="str">
         <x:v>tak</x:v>
@@ -787,7 +735,7 @@
       </x:c>
       <x:c r="C31"/>
       <x:c r="D31" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_11.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_11.webp</x:v>
       </x:c>
       <x:c r="E31" t="str">
         <x:v>tak</x:v>
@@ -803,7 +751,7 @@
       </x:c>
       <x:c r="C32"/>
       <x:c r="D32" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_12.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_12.webp</x:v>
       </x:c>
       <x:c r="E32" t="str">
         <x:v>tak</x:v>
@@ -819,7 +767,7 @@
       </x:c>
       <x:c r="C33"/>
       <x:c r="D33" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_13.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_13.webp</x:v>
       </x:c>
       <x:c r="E33" t="str">
         <x:v>tak</x:v>
@@ -835,7 +783,7 @@
       </x:c>
       <x:c r="C34"/>
       <x:c r="D34" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_15.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_15.webp</x:v>
       </x:c>
       <x:c r="E34" t="str">
         <x:v>tak</x:v>
@@ -851,7 +799,7 @@
       </x:c>
       <x:c r="C35"/>
       <x:c r="D35" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_16.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_16.webp</x:v>
       </x:c>
       <x:c r="E35" t="str">
         <x:v>tak</x:v>
@@ -867,7 +815,7 @@
       </x:c>
       <x:c r="C36"/>
       <x:c r="D36" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_17.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_17.webp</x:v>
       </x:c>
       <x:c r="E36" t="str">
         <x:v>tak</x:v>
@@ -883,7 +831,7 @@
       </x:c>
       <x:c r="C37"/>
       <x:c r="D37" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_18.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_18.webp</x:v>
       </x:c>
       <x:c r="E37" t="str">
         <x:v>tak</x:v>
@@ -899,7 +847,7 @@
       </x:c>
       <x:c r="C38"/>
       <x:c r="D38" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_19.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_19.webp</x:v>
       </x:c>
       <x:c r="E38" t="str">
         <x:v>tak</x:v>
@@ -915,7 +863,7 @@
       </x:c>
       <x:c r="C39"/>
       <x:c r="D39" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_20.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_20.webp</x:v>
       </x:c>
       <x:c r="E39" t="str">
         <x:v>tak</x:v>
@@ -931,7 +879,7 @@
       </x:c>
       <x:c r="C40"/>
       <x:c r="D40" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_21.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_21.webp</x:v>
       </x:c>
       <x:c r="E40" t="str">
         <x:v>tak</x:v>
@@ -947,7 +895,7 @@
       </x:c>
       <x:c r="C41"/>
       <x:c r="D41" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_22.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_22.webp</x:v>
       </x:c>
       <x:c r="E41" t="str">
         <x:v>tak</x:v>
@@ -963,7 +911,7 @@
       </x:c>
       <x:c r="C42"/>
       <x:c r="D42" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_23.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_23.webp</x:v>
       </x:c>
       <x:c r="E42" t="str">
         <x:v>tak</x:v>
@@ -979,7 +927,7 @@
       </x:c>
       <x:c r="C43"/>
       <x:c r="D43" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_24.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_24.webp</x:v>
       </x:c>
       <x:c r="E43" t="str">
         <x:v>tak</x:v>
@@ -995,7 +943,7 @@
       </x:c>
       <x:c r="C44"/>
       <x:c r="D44" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_25.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_25.webp</x:v>
       </x:c>
       <x:c r="E44" t="str">
         <x:v>tak</x:v>
@@ -1011,7 +959,7 @@
       </x:c>
       <x:c r="C45"/>
       <x:c r="D45" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_26.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_26.webp</x:v>
       </x:c>
       <x:c r="E45" t="str">
         <x:v>tak</x:v>
@@ -1027,7 +975,7 @@
       </x:c>
       <x:c r="C46"/>
       <x:c r="D46" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_27.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_27.webp</x:v>
       </x:c>
       <x:c r="E46" t="str">
         <x:v>tak</x:v>
@@ -1043,7 +991,7 @@
       </x:c>
       <x:c r="C47"/>
       <x:c r="D47" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_28.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_28.webp</x:v>
       </x:c>
       <x:c r="E47" t="str">
         <x:v>tak</x:v>
@@ -1059,7 +1007,7 @@
       </x:c>
       <x:c r="C48"/>
       <x:c r="D48" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_29.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_29.webp</x:v>
       </x:c>
       <x:c r="E48" t="str">
         <x:v>tak</x:v>
@@ -1075,7 +1023,7 @@
       </x:c>
       <x:c r="C49"/>
       <x:c r="D49" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_30.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_30.webp</x:v>
       </x:c>
       <x:c r="E49" t="str">
         <x:v>tak</x:v>
@@ -1091,7 +1039,7 @@
       </x:c>
       <x:c r="C50"/>
       <x:c r="D50" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_31.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczady/BIES_31.webp</x:v>
       </x:c>
       <x:c r="E50" t="str">
         <x:v>tak</x:v>
@@ -1107,7 +1055,7 @@
       </x:c>
       <x:c r="C51"/>
       <x:c r="D51" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzki klimat/BZWK_01_wilk.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzki klimat/BZWK_01_wilk.webp</x:v>
       </x:c>
       <x:c r="E51" t="str">
         <x:v>tak</x:v>
@@ -1123,7 +1071,7 @@
       </x:c>
       <x:c r="C52"/>
       <x:c r="D52" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzki klimat/BZWK_02_wilk.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzki klimat/BZWK_02_wilk.webp</x:v>
       </x:c>
       <x:c r="E52" t="str">
         <x:v>tak</x:v>
@@ -1139,7 +1087,7 @@
       </x:c>
       <x:c r="C53"/>
       <x:c r="D53" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzki klimat/BZWK_03_niedźwiedź.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzki klimat/BZWK_03_niedźwiedź.webp</x:v>
       </x:c>
       <x:c r="E53" t="str">
         <x:v>tak</x:v>
@@ -1155,7 +1103,7 @@
       </x:c>
       <x:c r="C54"/>
       <x:c r="D54" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzki klimat/BZWK_04_rys.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzki klimat/BZWK_04_rys.webp</x:v>
       </x:c>
       <x:c r="E54" t="str">
         <x:v>tak</x:v>
@@ -1171,7 +1119,7 @@
       </x:c>
       <x:c r="C55"/>
       <x:c r="D55" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzki klimat/BZWK_05_ żubr.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzki klimat/BZWK_05_ żubr.webp</x:v>
       </x:c>
       <x:c r="E55" t="str">
         <x:v>tak</x:v>
@@ -1187,7 +1135,7 @@
       </x:c>
       <x:c r="C56"/>
       <x:c r="D56" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzki klimat/BZWK_06_jeleń.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzki klimat/BZWK_06_jeleń.webp</x:v>
       </x:c>
       <x:c r="E56" t="str">
         <x:v>tak</x:v>
@@ -1203,7 +1151,7 @@
       </x:c>
       <x:c r="C57"/>
       <x:c r="D57" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzki klimat/BZWK_07_jastrząb.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzki klimat/BZWK_07_jastrząb.webp</x:v>
       </x:c>
       <x:c r="E57" t="str">
         <x:v>tak</x:v>
@@ -1219,7 +1167,7 @@
       </x:c>
       <x:c r="C58"/>
       <x:c r="D58" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_01.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_01.webp</x:v>
       </x:c>
       <x:c r="E58" t="str">
         <x:v>tak</x:v>
@@ -1235,7 +1183,7 @@
       </x:c>
       <x:c r="C59"/>
       <x:c r="D59" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_02.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_02.webp</x:v>
       </x:c>
       <x:c r="E59" t="str">
         <x:v>tak</x:v>
@@ -1251,7 +1199,7 @@
       </x:c>
       <x:c r="C60"/>
       <x:c r="D60" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_03.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_03.webp</x:v>
       </x:c>
       <x:c r="E60" t="str">
         <x:v>tak</x:v>
@@ -1267,7 +1215,7 @@
       </x:c>
       <x:c r="C61"/>
       <x:c r="D61" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_04.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_04.webp</x:v>
       </x:c>
       <x:c r="E61" t="str">
         <x:v>tak</x:v>
@@ -1283,7 +1231,7 @@
       </x:c>
       <x:c r="C62"/>
       <x:c r="D62" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_05.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_05.webp</x:v>
       </x:c>
       <x:c r="E62" t="str">
         <x:v>tak</x:v>
@@ -1299,7 +1247,7 @@
       </x:c>
       <x:c r="C63"/>
       <x:c r="D63" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_06.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_06.webp</x:v>
       </x:c>
       <x:c r="E63" t="str">
         <x:v>tak</x:v>
@@ -1315,7 +1263,7 @@
       </x:c>
       <x:c r="C64"/>
       <x:c r="D64" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_07.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_07.webp</x:v>
       </x:c>
       <x:c r="E64" t="str">
         <x:v>tak</x:v>
@@ -1331,7 +1279,7 @@
       </x:c>
       <x:c r="C65"/>
       <x:c r="D65" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_08.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_08.webp</x:v>
       </x:c>
       <x:c r="E65" t="str">
         <x:v>tak</x:v>
@@ -1347,7 +1295,7 @@
       </x:c>
       <x:c r="C66"/>
       <x:c r="D66" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_09.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_09.webp</x:v>
       </x:c>
       <x:c r="E66" t="str">
         <x:v>tak</x:v>
@@ -1363,7 +1311,7 @@
       </x:c>
       <x:c r="C67"/>
       <x:c r="D67" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_10.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_10.webp</x:v>
       </x:c>
       <x:c r="E67" t="str">
         <x:v>tak</x:v>
@@ -1379,7 +1327,7 @@
       </x:c>
       <x:c r="C68"/>
       <x:c r="D68" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_11.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_11.webp</x:v>
       </x:c>
       <x:c r="E68" t="str">
         <x:v>tak</x:v>
@@ -1395,7 +1343,7 @@
       </x:c>
       <x:c r="C69"/>
       <x:c r="D69" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_12.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_12.webp</x:v>
       </x:c>
       <x:c r="E69" t="str">
         <x:v>tak</x:v>
@@ -1411,7 +1359,7 @@
       </x:c>
       <x:c r="C70"/>
       <x:c r="D70" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_13.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_13.webp</x:v>
       </x:c>
       <x:c r="E70" t="str">
         <x:v>tak</x:v>
@@ -1427,7 +1375,7 @@
       </x:c>
       <x:c r="C71"/>
       <x:c r="D71" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_14.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_14.webp</x:v>
       </x:c>
       <x:c r="E71" t="str">
         <x:v>tak</x:v>
@@ -1443,7 +1391,7 @@
       </x:c>
       <x:c r="C72"/>
       <x:c r="D72" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_15.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_15.webp</x:v>
       </x:c>
       <x:c r="E72" t="str">
         <x:v>tak</x:v>
@@ -1459,7 +1407,7 @@
       </x:c>
       <x:c r="C73"/>
       <x:c r="D73" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_16.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_16.webp</x:v>
       </x:c>
       <x:c r="E73" t="str">
         <x:v>tak</x:v>
@@ -1475,7 +1423,7 @@
       </x:c>
       <x:c r="C74"/>
       <x:c r="D74" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_17.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_17.webp</x:v>
       </x:c>
       <x:c r="E74" t="str">
         <x:v>tak</x:v>
@@ -1491,7 +1439,7 @@
       </x:c>
       <x:c r="C75"/>
       <x:c r="D75" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_18.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_18.webp</x:v>
       </x:c>
       <x:c r="E75" t="str">
         <x:v>tak</x:v>
@@ -1507,7 +1455,7 @@
       </x:c>
       <x:c r="C76"/>
       <x:c r="D76" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_19.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_19.webp</x:v>
       </x:c>
       <x:c r="E76" t="str">
         <x:v>tak</x:v>
@@ -1523,7 +1471,7 @@
       </x:c>
       <x:c r="C77"/>
       <x:c r="D77" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_20.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_20.webp</x:v>
       </x:c>
       <x:c r="E77" t="str">
         <x:v>tak</x:v>
@@ -1539,7 +1487,7 @@
       </x:c>
       <x:c r="C78"/>
       <x:c r="D78" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_21.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_21.webp</x:v>
       </x:c>
       <x:c r="E78" t="str">
         <x:v>tak</x:v>
@@ -1555,7 +1503,7 @@
       </x:c>
       <x:c r="C79"/>
       <x:c r="D79" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_22.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_22.webp</x:v>
       </x:c>
       <x:c r="E79" t="str">
         <x:v>tak</x:v>
@@ -1571,7 +1519,7 @@
       </x:c>
       <x:c r="C80"/>
       <x:c r="D80" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_23.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_23.webp</x:v>
       </x:c>
       <x:c r="E80" t="str">
         <x:v>tak</x:v>
@@ -1587,7 +1535,7 @@
       </x:c>
       <x:c r="C81"/>
       <x:c r="D81" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_24.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_24.webp</x:v>
       </x:c>
       <x:c r="E81" t="str">
         <x:v>tak</x:v>
@@ -1603,7 +1551,7 @@
       </x:c>
       <x:c r="C82"/>
       <x:c r="D82" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_25.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_25.webp</x:v>
       </x:c>
       <x:c r="E82" t="str">
         <x:v>tak</x:v>
@@ -1619,7 +1567,7 @@
       </x:c>
       <x:c r="C83"/>
       <x:c r="D83" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_26.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_26.webp</x:v>
       </x:c>
       <x:c r="E83" t="str">
         <x:v>tak</x:v>
@@ -1635,7 +1583,7 @@
       </x:c>
       <x:c r="C84"/>
       <x:c r="D84" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_27.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_27.webp</x:v>
       </x:c>
       <x:c r="E84" t="str">
         <x:v>tak</x:v>
@@ -1651,7 +1599,7 @@
       </x:c>
       <x:c r="C85"/>
       <x:c r="D85" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_28.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_28.webp</x:v>
       </x:c>
       <x:c r="E85" t="str">
         <x:v>tak</x:v>
@@ -1667,7 +1615,7 @@
       </x:c>
       <x:c r="C86"/>
       <x:c r="D86" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_29.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_29.webp</x:v>
       </x:c>
       <x:c r="E86" t="str">
         <x:v>tak</x:v>
@@ -1683,7 +1631,7 @@
       </x:c>
       <x:c r="C87"/>
       <x:c r="D87" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_30.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_30.webp</x:v>
       </x:c>
       <x:c r="E87" t="str">
         <x:v>tak</x:v>
@@ -1699,7 +1647,7 @@
       </x:c>
       <x:c r="C88"/>
       <x:c r="D88" t="str">
-        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_31.png</x:v>
+        <x:v>zdjecia-produktow/torby/Bieszczadzkie zwierzęta/BIESZ_31.webp</x:v>
       </x:c>
       <x:c r="E88" t="str">
         <x:v>tak</x:v>
@@ -1715,7 +1663,7 @@
       </x:c>
       <x:c r="C89"/>
       <x:c r="D89" t="str">
-        <x:v>zdjecia-produktow/torby/Kolorowe Ptaki/KP_01.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kolorowe Ptaki/KP_01.webp</x:v>
       </x:c>
       <x:c r="E89" t="str">
         <x:v>tak</x:v>
@@ -1731,7 +1679,7 @@
       </x:c>
       <x:c r="C90"/>
       <x:c r="D90" t="str">
-        <x:v>zdjecia-produktow/torby/Kolorowe Ptaki/KP_02.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kolorowe Ptaki/KP_02.webp</x:v>
       </x:c>
       <x:c r="E90" t="str">
         <x:v>tak</x:v>
@@ -1747,7 +1695,7 @@
       </x:c>
       <x:c r="C91"/>
       <x:c r="D91" t="str">
-        <x:v>zdjecia-produktow/torby/Kolorowe Ptaki/KP_03.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kolorowe Ptaki/KP_03.webp</x:v>
       </x:c>
       <x:c r="E91" t="str">
         <x:v>tak</x:v>
@@ -1763,7 +1711,7 @@
       </x:c>
       <x:c r="C92"/>
       <x:c r="D92" t="str">
-        <x:v>zdjecia-produktow/torby/Kolorowe Ptaki/KP_04.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kolorowe Ptaki/KP_04.webp</x:v>
       </x:c>
       <x:c r="E92" t="str">
         <x:v>tak</x:v>
@@ -1779,7 +1727,7 @@
       </x:c>
       <x:c r="C93"/>
       <x:c r="D93" t="str">
-        <x:v>zdjecia-produktow/torby/Kolorowe Ptaki/KP_05.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kolorowe Ptaki/KP_05.webp</x:v>
       </x:c>
       <x:c r="E93" t="str">
         <x:v>tak</x:v>
@@ -1795,7 +1743,7 @@
       </x:c>
       <x:c r="C94"/>
       <x:c r="D94" t="str">
-        <x:v>zdjecia-produktow/torby/Kolorowe Ptaki/KP_06.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kolorowe Ptaki/KP_06.webp</x:v>
       </x:c>
       <x:c r="E94" t="str">
         <x:v>tak</x:v>
@@ -1811,7 +1759,7 @@
       </x:c>
       <x:c r="C95"/>
       <x:c r="D95" t="str">
-        <x:v>zdjecia-produktow/torby/Kolorowe Ptaki/KP_07.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kolorowe Ptaki/KP_07.webp</x:v>
       </x:c>
       <x:c r="E95" t="str">
         <x:v>tak</x:v>
@@ -1827,7 +1775,7 @@
       </x:c>
       <x:c r="C96"/>
       <x:c r="D96" t="str">
-        <x:v>zdjecia-produktow/torby/Kolorowe Ptaki/KP_08.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kolorowe Ptaki/KP_08.webp</x:v>
       </x:c>
       <x:c r="E96" t="str">
         <x:v>tak</x:v>
@@ -1843,7 +1791,7 @@
       </x:c>
       <x:c r="C97"/>
       <x:c r="D97" t="str">
-        <x:v>zdjecia-produktow/torby/Kolorowe Ptaki/KP_09.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kolorowe Ptaki/KP_09.webp</x:v>
       </x:c>
       <x:c r="E97" t="str">
         <x:v>tak</x:v>
@@ -1859,7 +1807,7 @@
       </x:c>
       <x:c r="C98"/>
       <x:c r="D98" t="str">
-        <x:v>zdjecia-produktow/torby/Kolorowe Ptaki/KP_10.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kolorowe Ptaki/KP_10.webp</x:v>
       </x:c>
       <x:c r="E98" t="str">
         <x:v>tak</x:v>
@@ -1875,7 +1823,7 @@
       </x:c>
       <x:c r="C99"/>
       <x:c r="D99" t="str">
-        <x:v>zdjecia-produktow/torby/Kolorowe Ptaki/KP_11.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kolorowe Ptaki/KP_11.webp</x:v>
       </x:c>
       <x:c r="E99" t="str">
         <x:v>tak</x:v>
@@ -1891,7 +1839,7 @@
       </x:c>
       <x:c r="C100"/>
       <x:c r="D100" t="str">
-        <x:v>zdjecia-produktow/torby/Kolorowe Ptaki/KP_12.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kolorowe Ptaki/KP_12.webp</x:v>
       </x:c>
       <x:c r="E100" t="str">
         <x:v>tak</x:v>
@@ -1907,7 +1855,7 @@
       </x:c>
       <x:c r="C101"/>
       <x:c r="D101" t="str">
-        <x:v>zdjecia-produktow/torby/Kolorowe Ptaki/KP_13.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kolorowe Ptaki/KP_13.webp</x:v>
       </x:c>
       <x:c r="E101" t="str">
         <x:v>tak</x:v>
@@ -1923,7 +1871,7 @@
       </x:c>
       <x:c r="C102"/>
       <x:c r="D102" t="str">
-        <x:v>zdjecia-produktow/torby/Kolorowe Ptaki/KP_14.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kolorowe Ptaki/KP_14.webp</x:v>
       </x:c>
       <x:c r="E102" t="str">
         <x:v>tak</x:v>
@@ -1939,7 +1887,7 @@
       </x:c>
       <x:c r="C103"/>
       <x:c r="D103" t="str">
-        <x:v>zdjecia-produktow/torby/Kolorowe Ptaki/KP_15.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kolorowe Ptaki/KP_15.webp</x:v>
       </x:c>
       <x:c r="E103" t="str">
         <x:v>tak</x:v>
@@ -1955,7 +1903,7 @@
       </x:c>
       <x:c r="C104"/>
       <x:c r="D104" t="str">
-        <x:v>zdjecia-produktow/torby/Kolorowe zwierzaki/KZ_01.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kolorowe zwierzaki/KZ_01.webp</x:v>
       </x:c>
       <x:c r="E104" t="str">
         <x:v>tak</x:v>
@@ -1971,7 +1919,7 @@
       </x:c>
       <x:c r="C105"/>
       <x:c r="D105" t="str">
-        <x:v>zdjecia-produktow/torby/Kolorowe zwierzaki/KZ_02.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kolorowe zwierzaki/KZ_02.webp</x:v>
       </x:c>
       <x:c r="E105" t="str">
         <x:v>tak</x:v>
@@ -1987,7 +1935,7 @@
       </x:c>
       <x:c r="C106"/>
       <x:c r="D106" t="str">
-        <x:v>zdjecia-produktow/torby/Kolorowe zwierzaki/KZ_03.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kolorowe zwierzaki/KZ_03.webp</x:v>
       </x:c>
       <x:c r="E106" t="str">
         <x:v>tak</x:v>
@@ -2003,7 +1951,7 @@
       </x:c>
       <x:c r="C107"/>
       <x:c r="D107" t="str">
-        <x:v>zdjecia-produktow/torby/Kolorowe zwierzaki/KZ_04.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kolorowe zwierzaki/KZ_04.webp</x:v>
       </x:c>
       <x:c r="E107" t="str">
         <x:v>tak</x:v>
@@ -2019,7 +1967,7 @@
       </x:c>
       <x:c r="C108"/>
       <x:c r="D108" t="str">
-        <x:v>zdjecia-produktow/torby/Kolorowe zwierzaki/KZ_05.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kolorowe zwierzaki/KZ_05.webp</x:v>
       </x:c>
       <x:c r="E108" t="str">
         <x:v>tak</x:v>
@@ -2035,7 +1983,7 @@
       </x:c>
       <x:c r="C109"/>
       <x:c r="D109" t="str">
-        <x:v>zdjecia-produktow/torby/Kolorowe zwierzaki/KZ_06.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kolorowe zwierzaki/KZ_06.webp</x:v>
       </x:c>
       <x:c r="E109" t="str">
         <x:v>tak</x:v>
@@ -2051,7 +1999,7 @@
       </x:c>
       <x:c r="C110"/>
       <x:c r="D110" t="str">
-        <x:v>zdjecia-produktow/torby/Kolorowe zwierzaki/KZ_07.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kolorowe zwierzaki/KZ_07.webp</x:v>
       </x:c>
       <x:c r="E110" t="str">
         <x:v>tak</x:v>
@@ -2067,7 +2015,7 @@
       </x:c>
       <x:c r="C111"/>
       <x:c r="D111" t="str">
-        <x:v>zdjecia-produktow/torby/Kolorowe zwierzaki/KZ_08.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kolorowe zwierzaki/KZ_08.webp</x:v>
       </x:c>
       <x:c r="E111" t="str">
         <x:v>tak</x:v>
@@ -2083,7 +2031,7 @@
       </x:c>
       <x:c r="C112"/>
       <x:c r="D112" t="str">
-        <x:v>zdjecia-produktow/torby/Kolorowe zwierzaki/KZ_09.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kolorowe zwierzaki/KZ_09.webp</x:v>
       </x:c>
       <x:c r="E112" t="str">
         <x:v>tak</x:v>
@@ -2099,7 +2047,7 @@
       </x:c>
       <x:c r="C113"/>
       <x:c r="D113" t="str">
-        <x:v>zdjecia-produktow/torby/Kolorowe zwierzaki/KZ_10.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kolorowe zwierzaki/KZ_10.webp</x:v>
       </x:c>
       <x:c r="E113" t="str">
         <x:v>tak</x:v>
@@ -2115,7 +2063,7 @@
       </x:c>
       <x:c r="C114"/>
       <x:c r="D114" t="str">
-        <x:v>zdjecia-produktow/torby/Kolorowe zwierzaki/KZ_11.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kolorowe zwierzaki/KZ_11.webp</x:v>
       </x:c>
       <x:c r="E114" t="str">
         <x:v>tak</x:v>
@@ -2131,7 +2079,7 @@
       </x:c>
       <x:c r="C115"/>
       <x:c r="D115" t="str">
-        <x:v>zdjecia-produktow/torby/Kolorowe zwierzaki/KZ_12.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kolorowe zwierzaki/KZ_12.webp</x:v>
       </x:c>
       <x:c r="E115" t="str">
         <x:v>tak</x:v>
@@ -2147,7 +2095,7 @@
       </x:c>
       <x:c r="C116"/>
       <x:c r="D116" t="str">
-        <x:v>zdjecia-produktow/torby/Kolorowe zwierzaki/KZ_13.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kolorowe zwierzaki/KZ_13.webp</x:v>
       </x:c>
       <x:c r="E116" t="str">
         <x:v>tak</x:v>
@@ -2163,7 +2111,7 @@
       </x:c>
       <x:c r="C117"/>
       <x:c r="D117" t="str">
-        <x:v>zdjecia-produktow/torby/Kolorowe zwierzaki/KZ_14.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kolorowe zwierzaki/KZ_14.webp</x:v>
       </x:c>
       <x:c r="E117" t="str">
         <x:v>tak</x:v>
@@ -2179,7 +2127,7 @@
       </x:c>
       <x:c r="C118"/>
       <x:c r="D118" t="str">
-        <x:v>zdjecia-produktow/torby/Kolorowe zwierzaki/KZ_15.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kolorowe zwierzaki/KZ_15.webp</x:v>
       </x:c>
       <x:c r="E118" t="str">
         <x:v>tak</x:v>
@@ -2195,7 +2143,7 @@
       </x:c>
       <x:c r="C119"/>
       <x:c r="D119" t="str">
-        <x:v>zdjecia-produktow/torby/Kolorowe zwierzaki/KZ_16.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kolorowe zwierzaki/KZ_16.webp</x:v>
       </x:c>
       <x:c r="E119" t="str">
         <x:v>tak</x:v>
@@ -2211,7 +2159,7 @@
       </x:c>
       <x:c r="C120"/>
       <x:c r="D120" t="str">
-        <x:v>zdjecia-produktow/torby/Kolorowe zwierzaki/KZ_17.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kolorowe zwierzaki/KZ_17.webp</x:v>
       </x:c>
       <x:c r="E120" t="str">
         <x:v>tak</x:v>
@@ -2227,7 +2175,7 @@
       </x:c>
       <x:c r="C121"/>
       <x:c r="D121" t="str">
-        <x:v>zdjecia-produktow/torby/Kolorowe zwierzaki/KZ_18.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kolorowe zwierzaki/KZ_18.webp</x:v>
       </x:c>
       <x:c r="E121" t="str">
         <x:v>tak</x:v>
@@ -2243,7 +2191,7 @@
       </x:c>
       <x:c r="C122"/>
       <x:c r="D122" t="str">
-        <x:v>zdjecia-produktow/torby/Konie/KO_01.png</x:v>
+        <x:v>zdjecia-produktow/torby/Konie/KO_01.webp</x:v>
       </x:c>
       <x:c r="E122" t="str">
         <x:v>tak</x:v>
@@ -2259,7 +2207,7 @@
       </x:c>
       <x:c r="C123"/>
       <x:c r="D123" t="str">
-        <x:v>zdjecia-produktow/torby/Konie/KO_02.png</x:v>
+        <x:v>zdjecia-produktow/torby/Konie/KO_02.webp</x:v>
       </x:c>
       <x:c r="E123" t="str">
         <x:v>tak</x:v>
@@ -2275,7 +2223,7 @@
       </x:c>
       <x:c r="C124"/>
       <x:c r="D124" t="str">
-        <x:v>zdjecia-produktow/torby/Konie/KO_03.png</x:v>
+        <x:v>zdjecia-produktow/torby/Konie/KO_03.webp</x:v>
       </x:c>
       <x:c r="E124" t="str">
         <x:v>tak</x:v>
@@ -2291,7 +2239,7 @@
       </x:c>
       <x:c r="C125"/>
       <x:c r="D125" t="str">
-        <x:v>zdjecia-produktow/torby/Kwiaty/KW_01.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kwiaty/KW_01.webp</x:v>
       </x:c>
       <x:c r="E125" t="str">
         <x:v>tak</x:v>
@@ -2307,7 +2255,7 @@
       </x:c>
       <x:c r="C126"/>
       <x:c r="D126" t="str">
-        <x:v>zdjecia-produktow/torby/Kwiaty/KW_02.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kwiaty/KW_02.webp</x:v>
       </x:c>
       <x:c r="E126" t="str">
         <x:v>tak</x:v>
@@ -2323,7 +2271,7 @@
       </x:c>
       <x:c r="C127"/>
       <x:c r="D127" t="str">
-        <x:v>zdjecia-produktow/torby/Kwiaty/KW_03.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kwiaty/KW_03.webp</x:v>
       </x:c>
       <x:c r="E127" t="str">
         <x:v>tak</x:v>
@@ -2339,7 +2287,7 @@
       </x:c>
       <x:c r="C128"/>
       <x:c r="D128" t="str">
-        <x:v>zdjecia-produktow/torby/Kwiaty/KW_04.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kwiaty/KW_04.webp</x:v>
       </x:c>
       <x:c r="E128" t="str">
         <x:v>tak</x:v>
@@ -2355,7 +2303,7 @@
       </x:c>
       <x:c r="C129"/>
       <x:c r="D129" t="str">
-        <x:v>zdjecia-produktow/torby/Kwiaty/KW_05.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kwiaty/KW_05.webp</x:v>
       </x:c>
       <x:c r="E129" t="str">
         <x:v>tak</x:v>
@@ -2371,7 +2319,7 @@
       </x:c>
       <x:c r="C130"/>
       <x:c r="D130" t="str">
-        <x:v>zdjecia-produktow/torby/Kwiaty/KW_06.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kwiaty/KW_06.webp</x:v>
       </x:c>
       <x:c r="E130" t="str">
         <x:v>tak</x:v>
@@ -2387,7 +2335,7 @@
       </x:c>
       <x:c r="C131"/>
       <x:c r="D131" t="str">
-        <x:v>zdjecia-produktow/torby/Kwiaty/KW_07.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kwiaty/KW_07.webp</x:v>
       </x:c>
       <x:c r="E131" t="str">
         <x:v>tak</x:v>
@@ -2403,7 +2351,7 @@
       </x:c>
       <x:c r="C132"/>
       <x:c r="D132" t="str">
-        <x:v>zdjecia-produktow/torby/Kwiaty/KW_08.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kwiaty/KW_08.webp</x:v>
       </x:c>
       <x:c r="E132" t="str">
         <x:v>tak</x:v>
@@ -2419,7 +2367,7 @@
       </x:c>
       <x:c r="C133"/>
       <x:c r="D133" t="str">
-        <x:v>zdjecia-produktow/torby/Kwiaty/KW_09.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kwiaty/KW_09.webp</x:v>
       </x:c>
       <x:c r="E133" t="str">
         <x:v>tak</x:v>
@@ -2435,7 +2383,7 @@
       </x:c>
       <x:c r="C134"/>
       <x:c r="D134" t="str">
-        <x:v>zdjecia-produktow/torby/Kwiaty/KW_10.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kwiaty/KW_10.webp</x:v>
       </x:c>
       <x:c r="E134" t="str">
         <x:v>tak</x:v>
@@ -2451,7 +2399,7 @@
       </x:c>
       <x:c r="C135"/>
       <x:c r="D135" t="str">
-        <x:v>zdjecia-produktow/torby/Kwiaty/KW_11.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kwiaty/KW_11.webp</x:v>
       </x:c>
       <x:c r="E135" t="str">
         <x:v>tak</x:v>
@@ -2467,7 +2415,7 @@
       </x:c>
       <x:c r="C136"/>
       <x:c r="D136" t="str">
-        <x:v>zdjecia-produktow/torby/Kwiaty/KW_12.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kwiaty/KW_12.webp</x:v>
       </x:c>
       <x:c r="E136" t="str">
         <x:v>tak</x:v>
@@ -2483,7 +2431,7 @@
       </x:c>
       <x:c r="C137"/>
       <x:c r="D137" t="str">
-        <x:v>zdjecia-produktow/torby/Kwiaty/KW_13.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kwiaty/KW_13.webp</x:v>
       </x:c>
       <x:c r="E137" t="str">
         <x:v>tak</x:v>
@@ -2499,7 +2447,7 @@
       </x:c>
       <x:c r="C138"/>
       <x:c r="D138" t="str">
-        <x:v>zdjecia-produktow/torby/Kwiaty/KW_14.png</x:v>
+        <x:v>zdjecia-produktow/torby/Kwiaty/KW_14.webp</x:v>
       </x:c>
       <x:c r="E138" t="str">
         <x:v>tak</x:v>
@@ -2515,10 +2463,10 @@
       </x:c>
       <x:c r="C139"/>
       <x:c r="D139" t="str">
-        <x:v>zdjecia-produktow/torby/Miasta/LESKO.png</x:v>
+        <x:v>zdjecia-produktow/torby/Miasta/LESKO.webp</x:v>
       </x:c>
       <x:c r="E139" t="str">
-        <x:v>tak</x:v>
+        <x:v>nie</x:v>
       </x:c>
       <x:c r="F139"/>
     </x:row>
@@ -2531,10 +2479,10 @@
       </x:c>
       <x:c r="C140"/>
       <x:c r="D140" t="str">
-        <x:v>zdjecia-produktow/torby/Miasta/SANOK.png</x:v>
+        <x:v>zdjecia-produktow/torby/Miasta/SANOK.webp</x:v>
       </x:c>
       <x:c r="E140" t="str">
-        <x:v>tak</x:v>
+        <x:v>nie</x:v>
       </x:c>
       <x:c r="F140"/>
     </x:row>
@@ -2547,10 +2495,10 @@
       </x:c>
       <x:c r="C141"/>
       <x:c r="D141" t="str">
-        <x:v>zdjecia-produktow/torby/Miasta/ZAGÓRZ.png</x:v>
+        <x:v>zdjecia-produktow/torby/Miasta/ZAGÓRZ.webp</x:v>
       </x:c>
       <x:c r="E141" t="str">
-        <x:v>tak</x:v>
+        <x:v>nie</x:v>
       </x:c>
       <x:c r="F141"/>
     </x:row>
@@ -2563,7 +2511,7 @@
       </x:c>
       <x:c r="C142"/>
       <x:c r="D142" t="str">
-        <x:v>zdjecia-produktow/torby/Motoryzacja/MOTO_01.png</x:v>
+        <x:v>zdjecia-produktow/torby/Motoryzacja/MOTO_01.webp</x:v>
       </x:c>
       <x:c r="E142" t="str">
         <x:v>tak</x:v>
@@ -2579,7 +2527,7 @@
       </x:c>
       <x:c r="C143"/>
       <x:c r="D143" t="str">
-        <x:v>zdjecia-produktow/torby/Motoryzacja/MOTO_02.png</x:v>
+        <x:v>zdjecia-produktow/torby/Motoryzacja/MOTO_02.webp</x:v>
       </x:c>
       <x:c r="E143" t="str">
         <x:v>tak</x:v>
@@ -2595,7 +2543,7 @@
       </x:c>
       <x:c r="C144"/>
       <x:c r="D144" t="str">
-        <x:v>zdjecia-produktow/torby/Motoryzacja/MOTO_03.png</x:v>
+        <x:v>zdjecia-produktow/torby/Motoryzacja/MOTO_03.webp</x:v>
       </x:c>
       <x:c r="E144" t="str">
         <x:v>tak</x:v>
@@ -2611,7 +2559,7 @@
       </x:c>
       <x:c r="C145"/>
       <x:c r="D145" t="str">
-        <x:v>zdjecia-produktow/torby/Motoryzacja/MOTO_04.png</x:v>
+        <x:v>zdjecia-produktow/torby/Motoryzacja/MOTO_04.webp</x:v>
       </x:c>
       <x:c r="E145" t="str">
         <x:v>tak</x:v>
@@ -2627,7 +2575,7 @@
       </x:c>
       <x:c r="C146"/>
       <x:c r="D146" t="str">
-        <x:v>zdjecia-produktow/torby/Owady/OW_01.png</x:v>
+        <x:v>zdjecia-produktow/torby/Owady/OW_01.webp</x:v>
       </x:c>
       <x:c r="E146" t="str">
         <x:v>tak</x:v>
@@ -2643,7 +2591,7 @@
       </x:c>
       <x:c r="C147"/>
       <x:c r="D147" t="str">
-        <x:v>zdjecia-produktow/torby/Owady/OW_02.png</x:v>
+        <x:v>zdjecia-produktow/torby/Owady/OW_02.webp</x:v>
       </x:c>
       <x:c r="E147" t="str">
         <x:v>tak</x:v>
@@ -2659,7 +2607,7 @@
       </x:c>
       <x:c r="C148"/>
       <x:c r="D148" t="str">
-        <x:v>zdjecia-produktow/torby/Owady/OW_03.png</x:v>
+        <x:v>zdjecia-produktow/torby/Owady/OW_03.webp</x:v>
       </x:c>
       <x:c r="E148" t="str">
         <x:v>tak</x:v>
@@ -2675,7 +2623,7 @@
       </x:c>
       <x:c r="C149"/>
       <x:c r="D149" t="str">
-        <x:v>zdjecia-produktow/torby/Owady/OW_04.png</x:v>
+        <x:v>zdjecia-produktow/torby/Owady/OW_04.webp</x:v>
       </x:c>
       <x:c r="E149" t="str">
         <x:v>tak</x:v>
@@ -2691,7 +2639,7 @@
       </x:c>
       <x:c r="C150"/>
       <x:c r="D150" t="str">
-        <x:v>zdjecia-produktow/torby/Owady/OW_05.png</x:v>
+        <x:v>zdjecia-produktow/torby/Owady/OW_05.webp</x:v>
       </x:c>
       <x:c r="E150" t="str">
         <x:v>tak</x:v>
@@ -2707,7 +2655,7 @@
       </x:c>
       <x:c r="C151"/>
       <x:c r="D151" t="str">
-        <x:v>zdjecia-produktow/torby/Owady/OW_06.png</x:v>
+        <x:v>zdjecia-produktow/torby/Owady/OW_06.webp</x:v>
       </x:c>
       <x:c r="E151" t="str">
         <x:v>tak</x:v>
@@ -2723,7 +2671,7 @@
       </x:c>
       <x:c r="C152"/>
       <x:c r="D152" t="str">
-        <x:v>zdjecia-produktow/torby/Owady/OW_07.png</x:v>
+        <x:v>zdjecia-produktow/torby/Owady/OW_07.webp</x:v>
       </x:c>
       <x:c r="E152" t="str">
         <x:v>tak</x:v>
@@ -2739,7 +2687,7 @@
       </x:c>
       <x:c r="C153"/>
       <x:c r="D153" t="str">
-        <x:v>zdjecia-produktow/torby/Owady/OW_08.png</x:v>
+        <x:v>zdjecia-produktow/torby/Owady/OW_08.webp</x:v>
       </x:c>
       <x:c r="E153" t="str">
         <x:v>tak</x:v>
@@ -2755,7 +2703,7 @@
       </x:c>
       <x:c r="C154"/>
       <x:c r="D154" t="str">
-        <x:v>zdjecia-produktow/torby/Owady/OW_09.png</x:v>
+        <x:v>zdjecia-produktow/torby/Owady/OW_09.webp</x:v>
       </x:c>
       <x:c r="E154" t="str">
         <x:v>tak</x:v>
@@ -2771,7 +2719,7 @@
       </x:c>
       <x:c r="C155"/>
       <x:c r="D155" t="str">
-        <x:v>zdjecia-produktow/torby/Owady/OW_10.png</x:v>
+        <x:v>zdjecia-produktow/torby/Owady/OW_10.webp</x:v>
       </x:c>
       <x:c r="E155" t="str">
         <x:v>tak</x:v>
@@ -2787,7 +2735,7 @@
       </x:c>
       <x:c r="C156"/>
       <x:c r="D156" t="str">
-        <x:v>zdjecia-produktow/torby/Owady/OW_11.png</x:v>
+        <x:v>zdjecia-produktow/torby/Owady/OW_11.webp</x:v>
       </x:c>
       <x:c r="E156" t="str">
         <x:v>tak</x:v>
@@ -2803,7 +2751,7 @@
       </x:c>
       <x:c r="C157"/>
       <x:c r="D157" t="str">
-        <x:v>zdjecia-produktow/torby/Owady/OW_12.png</x:v>
+        <x:v>zdjecia-produktow/torby/Owady/OW_12.webp</x:v>
       </x:c>
       <x:c r="E157" t="str">
         <x:v>tak</x:v>
@@ -2819,7 +2767,7 @@
       </x:c>
       <x:c r="C158"/>
       <x:c r="D158" t="str">
-        <x:v>zdjecia-produktow/torby/Owady/OW_13.png</x:v>
+        <x:v>zdjecia-produktow/torby/Owady/OW_13.webp</x:v>
       </x:c>
       <x:c r="E158" t="str">
         <x:v>tak</x:v>
@@ -2835,7 +2783,7 @@
       </x:c>
       <x:c r="C159"/>
       <x:c r="D159" t="str">
-        <x:v>zdjecia-produktow/torby/Retro Bieszczady/BRET_01.png</x:v>
+        <x:v>zdjecia-produktow/torby/Retro Bieszczady/BRET_01.webp</x:v>
       </x:c>
       <x:c r="E159" t="str">
         <x:v>tak</x:v>
@@ -2851,7 +2799,7 @@
       </x:c>
       <x:c r="C160"/>
       <x:c r="D160" t="str">
-        <x:v>zdjecia-produktow/torby/Retro Bieszczady/BRET_02.png</x:v>
+        <x:v>zdjecia-produktow/torby/Retro Bieszczady/BRET_02.webp</x:v>
       </x:c>
       <x:c r="E160" t="str">
         <x:v>tak</x:v>
@@ -2867,7 +2815,7 @@
       </x:c>
       <x:c r="C161"/>
       <x:c r="D161" t="str">
-        <x:v>zdjecia-produktow/torby/Retro Bieszczady/BRET_03.png</x:v>
+        <x:v>zdjecia-produktow/torby/Retro Bieszczady/BRET_03.webp</x:v>
       </x:c>
       <x:c r="E161" t="str">
         <x:v>tak</x:v>
@@ -2883,7 +2831,7 @@
       </x:c>
       <x:c r="C162"/>
       <x:c r="D162" t="str">
-        <x:v>zdjecia-produktow/torby/Retro Bieszczady/BRET_04.png</x:v>
+        <x:v>zdjecia-produktow/torby/Retro Bieszczady/BRET_04.webp</x:v>
       </x:c>
       <x:c r="E162" t="str">
         <x:v>tak</x:v>
@@ -2899,7 +2847,7 @@
       </x:c>
       <x:c r="C163"/>
       <x:c r="D163" t="str">
-        <x:v>zdjecia-produktow/torby/Retro Bieszczady/BRET_05.png</x:v>
+        <x:v>zdjecia-produktow/torby/Retro Bieszczady/BRET_05.webp</x:v>
       </x:c>
       <x:c r="E163" t="str">
         <x:v>tak</x:v>
@@ -2915,7 +2863,7 @@
       </x:c>
       <x:c r="C164"/>
       <x:c r="D164" t="str">
-        <x:v>zdjecia-produktow/torby/Rzuć wszystko i jedź w Bieszczady/RZWB_01.PNG</x:v>
+        <x:v>zdjecia-produktow/torby/Rzuć wszystko i jedź w Bieszczady/RZWB_01.jpg</x:v>
       </x:c>
       <x:c r="E164" t="str">
         <x:v>tak</x:v>
@@ -2931,7 +2879,7 @@
       </x:c>
       <x:c r="C165"/>
       <x:c r="D165" t="str">
-        <x:v>zdjecia-produktow/torby/Rzuć wszystko i jedź w Bieszczady/RZWB_02.PNG</x:v>
+        <x:v>zdjecia-produktow/torby/Rzuć wszystko i jedź w Bieszczady/RZWB_02.jpg</x:v>
       </x:c>
       <x:c r="E165" t="str">
         <x:v>tak</x:v>
@@ -2947,7 +2895,7 @@
       </x:c>
       <x:c r="C166"/>
       <x:c r="D166" t="str">
-        <x:v>zdjecia-produktow/torby/Rzuć wszystko i jedź w Bieszczady/RZWB_03.png</x:v>
+        <x:v>zdjecia-produktow/torby/Rzuć wszystko i jedź w Bieszczady/RZWB_03.jpg</x:v>
       </x:c>
       <x:c r="E166" t="str">
         <x:v>tak</x:v>
@@ -2963,7 +2911,7 @@
       </x:c>
       <x:c r="C167"/>
       <x:c r="D167" t="str">
-        <x:v>zdjecia-produktow/torby/Rzuć wszystko i jedź w Bieszczady/RZWB_04.png</x:v>
+        <x:v>zdjecia-produktow/torby/Rzuć wszystko i jedź w Bieszczady/RZWB_04.jpg</x:v>
       </x:c>
       <x:c r="E167" t="str">
         <x:v>tak</x:v>
@@ -2979,7 +2927,7 @@
       </x:c>
       <x:c r="C168"/>
       <x:c r="D168" t="str">
-        <x:v>zdjecia-produktow/torby/Rzuć wszystko i jedź w Bieszczady/RZWB_05.png</x:v>
+        <x:v>zdjecia-produktow/torby/Rzuć wszystko i jedź w Bieszczady/RZWB_05.jpg</x:v>
       </x:c>
       <x:c r="E168" t="str">
         <x:v>tak</x:v>
@@ -2995,7 +2943,7 @@
       </x:c>
       <x:c r="C169"/>
       <x:c r="D169" t="str">
-        <x:v>zdjecia-produktow/torby/Rzuć wszystko i jedź w Bieszczady/RZWB_06.png</x:v>
+        <x:v>zdjecia-produktow/torby/Rzuć wszystko i jedź w Bieszczady/RZWB_06.jpg</x:v>
       </x:c>
       <x:c r="E169" t="str">
         <x:v>tak</x:v>
@@ -3011,7 +2959,7 @@
       </x:c>
       <x:c r="C170"/>
       <x:c r="D170" t="str">
-        <x:v>zdjecia-produktow/torby/Rzuć wszystko i jedź w Bieszczady/RZWB_07.png</x:v>
+        <x:v>zdjecia-produktow/torby/Rzuć wszystko i jedź w Bieszczady/RZWB_07.jpg</x:v>
       </x:c>
       <x:c r="E170" t="str">
         <x:v>tak</x:v>
@@ -3027,7 +2975,7 @@
       </x:c>
       <x:c r="C171"/>
       <x:c r="D171" t="str">
-        <x:v>zdjecia-produktow/torby/Rzuć wszystko i jedź w Bieszczady/RZWB_08.png</x:v>
+        <x:v>zdjecia-produktow/torby/Rzuć wszystko i jedź w Bieszczady/RZWB_08.jpg</x:v>
       </x:c>
       <x:c r="E171" t="str">
         <x:v>tak</x:v>
@@ -3043,7 +2991,7 @@
       </x:c>
       <x:c r="C172"/>
       <x:c r="D172" t="str">
-        <x:v>zdjecia-produktow/torby/Rzuć wszystko i jedź w Bieszczady/RZWB_09.png</x:v>
+        <x:v>zdjecia-produktow/torby/Rzuć wszystko i jedź w Bieszczady/RZWB_09.jpg</x:v>
       </x:c>
       <x:c r="E172" t="str">
         <x:v>tak</x:v>
@@ -3059,7 +3007,7 @@
       </x:c>
       <x:c r="C173"/>
       <x:c r="D173" t="str">
-        <x:v>zdjecia-produktow/torby/Rzuć wszystko i jedź w Bieszczady/RZWB_10.png</x:v>
+        <x:v>zdjecia-produktow/torby/Rzuć wszystko i jedź w Bieszczady/RZWB_10.jpg</x:v>
       </x:c>
       <x:c r="E173" t="str">
         <x:v>tak</x:v>
@@ -3075,7 +3023,7 @@
       </x:c>
       <x:c r="C174"/>
       <x:c r="D174" t="str">
-        <x:v>zdjecia-produktow/torby/Rzuć wszystko i jedź w Bieszczady/RZWB_11.png</x:v>
+        <x:v>zdjecia-produktow/torby/Rzuć wszystko i jedź w Bieszczady/RZWB_11.jpg</x:v>
       </x:c>
       <x:c r="E174" t="str">
         <x:v>tak</x:v>
@@ -3091,7 +3039,7 @@
       </x:c>
       <x:c r="C175"/>
       <x:c r="D175" t="str">
-        <x:v>zdjecia-produktow/torby/Rzuć wszystko i jedź w Bieszczady/RZWB_12.png</x:v>
+        <x:v>zdjecia-produktow/torby/Rzuć wszystko i jedź w Bieszczady/RZWB_12.jpg</x:v>
       </x:c>
       <x:c r="E175" t="str">
         <x:v>tak</x:v>
@@ -3107,7 +3055,7 @@
       </x:c>
       <x:c r="C176"/>
       <x:c r="D176" t="str">
-        <x:v>zdjecia-produktow/torby/Rzuć wszystko i jedź w Bieszczady/RZWB_13.png</x:v>
+        <x:v>zdjecia-produktow/torby/Rzuć wszystko i jedź w Bieszczady/RZWB_13.jpg</x:v>
       </x:c>
       <x:c r="E176" t="str">
         <x:v>tak</x:v>
@@ -3123,7 +3071,7 @@
       </x:c>
       <x:c r="C177"/>
       <x:c r="D177" t="str">
-        <x:v>zdjecia-produktow/torby/Rzuć wszystko i jedź w Bieszczady/RZWB_14.png</x:v>
+        <x:v>zdjecia-produktow/torby/Rzuć wszystko i jedź w Bieszczady/RZWB_14.jpg</x:v>
       </x:c>
       <x:c r="E177" t="str">
         <x:v>tak</x:v>
@@ -3139,7 +3087,7 @@
       </x:c>
       <x:c r="C178"/>
       <x:c r="D178" t="str">
-        <x:v>zdjecia-produktow/torby/Rzuć wszystko i jedź w Bieszczady/RZWB_15.png</x:v>
+        <x:v>zdjecia-produktow/torby/Rzuć wszystko i jedź w Bieszczady/RZWB_15.jpg</x:v>
       </x:c>
       <x:c r="E178" t="str">
         <x:v>tak</x:v>
@@ -3155,7 +3103,7 @@
       </x:c>
       <x:c r="C179"/>
       <x:c r="D179" t="str">
-        <x:v>zdjecia-produktow/torby/Rzuć wszystko i jedź w Bieszczady/RZWB_16.png</x:v>
+        <x:v>zdjecia-produktow/torby/Rzuć wszystko i jedź w Bieszczady/RZWB_16.jpg</x:v>
       </x:c>
       <x:c r="E179" t="str">
         <x:v>tak</x:v>
@@ -3171,7 +3119,7 @@
       </x:c>
       <x:c r="C180"/>
       <x:c r="D180" t="str">
-        <x:v>zdjecia-produktow/torby/Warzywa/WAR_01.png</x:v>
+        <x:v>zdjecia-produktow/torby/Warzywa/WAR_01.webp</x:v>
       </x:c>
       <x:c r="E180" t="str">
         <x:v>tak</x:v>
@@ -3187,7 +3135,7 @@
       </x:c>
       <x:c r="C181"/>
       <x:c r="D181" t="str">
-        <x:v>zdjecia-produktow/torby/Warzywa/WAR_02.png</x:v>
+        <x:v>zdjecia-produktow/torby/Warzywa/WAR_02.webp</x:v>
       </x:c>
       <x:c r="E181" t="str">
         <x:v>tak</x:v>
@@ -3203,7 +3151,7 @@
       </x:c>
       <x:c r="C182"/>
       <x:c r="D182" t="str">
-        <x:v>zdjecia-produktow/torby/Warzywa/WAR_03.png</x:v>
+        <x:v>zdjecia-produktow/torby/Warzywa/WAR_03.webp</x:v>
       </x:c>
       <x:c r="E182" t="str">
         <x:v>tak</x:v>
@@ -3219,7 +3167,7 @@
       </x:c>
       <x:c r="C183"/>
       <x:c r="D183" t="str">
-        <x:v>zdjecia-produktow/torby/Warzywa/WAR_04.png</x:v>
+        <x:v>zdjecia-produktow/torby/Warzywa/WAR_04.webp</x:v>
       </x:c>
       <x:c r="E183" t="str">
         <x:v>tak</x:v>
@@ -3235,7 +3183,7 @@
       </x:c>
       <x:c r="C184"/>
       <x:c r="D184" t="str">
-        <x:v>zdjecia-produktow/torby/Warzywa/WAR_05.png</x:v>
+        <x:v>zdjecia-produktow/torby/Warzywa/WAR_05.webp</x:v>
       </x:c>
       <x:c r="E184" t="str">
         <x:v>tak</x:v>
@@ -3251,7 +3199,7 @@
       </x:c>
       <x:c r="C185"/>
       <x:c r="D185" t="str">
-        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_01.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_01.webp</x:v>
       </x:c>
       <x:c r="E185" t="str">
         <x:v>tak</x:v>
@@ -3267,7 +3215,7 @@
       </x:c>
       <x:c r="C186"/>
       <x:c r="D186" t="str">
-        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_02.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_02.webp</x:v>
       </x:c>
       <x:c r="E186" t="str">
         <x:v>tak</x:v>
@@ -3283,7 +3231,7 @@
       </x:c>
       <x:c r="C187"/>
       <x:c r="D187" t="str">
-        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_03.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_03.webp</x:v>
       </x:c>
       <x:c r="E187" t="str">
         <x:v>tak</x:v>
@@ -3299,7 +3247,7 @@
       </x:c>
       <x:c r="C188"/>
       <x:c r="D188" t="str">
-        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_04.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_04.webp</x:v>
       </x:c>
       <x:c r="E188" t="str">
         <x:v>tak</x:v>
@@ -3315,7 +3263,7 @@
       </x:c>
       <x:c r="C189"/>
       <x:c r="D189" t="str">
-        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_05.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_05.webp</x:v>
       </x:c>
       <x:c r="E189" t="str">
         <x:v>tak</x:v>
@@ -3331,7 +3279,7 @@
       </x:c>
       <x:c r="C190"/>
       <x:c r="D190" t="str">
-        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_06.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_06.webp</x:v>
       </x:c>
       <x:c r="E190" t="str">
         <x:v>tak</x:v>
@@ -3347,7 +3295,7 @@
       </x:c>
       <x:c r="C191"/>
       <x:c r="D191" t="str">
-        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_07.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_07.webp</x:v>
       </x:c>
       <x:c r="E191" t="str">
         <x:v>tak</x:v>
@@ -3363,7 +3311,7 @@
       </x:c>
       <x:c r="C192"/>
       <x:c r="D192" t="str">
-        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_08.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_08.webp</x:v>
       </x:c>
       <x:c r="E192" t="str">
         <x:v>tak</x:v>
@@ -3379,7 +3327,7 @@
       </x:c>
       <x:c r="C193"/>
       <x:c r="D193" t="str">
-        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_09.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_09.webp</x:v>
       </x:c>
       <x:c r="E193" t="str">
         <x:v>tak</x:v>
@@ -3395,7 +3343,7 @@
       </x:c>
       <x:c r="C194"/>
       <x:c r="D194" t="str">
-        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_10.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_10.webp</x:v>
       </x:c>
       <x:c r="E194" t="str">
         <x:v>tak</x:v>
@@ -3411,7 +3359,7 @@
       </x:c>
       <x:c r="C195"/>
       <x:c r="D195" t="str">
-        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_11.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_11.webp</x:v>
       </x:c>
       <x:c r="E195" t="str">
         <x:v>tak</x:v>
@@ -3427,7 +3375,7 @@
       </x:c>
       <x:c r="C196"/>
       <x:c r="D196" t="str">
-        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_12.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_12.webp</x:v>
       </x:c>
       <x:c r="E196" t="str">
         <x:v>tak</x:v>
@@ -3443,7 +3391,7 @@
       </x:c>
       <x:c r="C197"/>
       <x:c r="D197" t="str">
-        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_13.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_13.webp</x:v>
       </x:c>
       <x:c r="E197" t="str">
         <x:v>tak</x:v>
@@ -3459,7 +3407,7 @@
       </x:c>
       <x:c r="C198"/>
       <x:c r="D198" t="str">
-        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_14.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_14.webp</x:v>
       </x:c>
       <x:c r="E198" t="str">
         <x:v>tak</x:v>
@@ -3475,7 +3423,7 @@
       </x:c>
       <x:c r="C199"/>
       <x:c r="D199" t="str">
-        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_15.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_15.webp</x:v>
       </x:c>
       <x:c r="E199" t="str">
         <x:v>tak</x:v>
@@ -3491,7 +3439,7 @@
       </x:c>
       <x:c r="C200"/>
       <x:c r="D200" t="str">
-        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_16.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_16.webp</x:v>
       </x:c>
       <x:c r="E200" t="str">
         <x:v>tak</x:v>
@@ -3507,7 +3455,7 @@
       </x:c>
       <x:c r="C201"/>
       <x:c r="D201" t="str">
-        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_17.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_17.webp</x:v>
       </x:c>
       <x:c r="E201" t="str">
         <x:v>tak</x:v>
@@ -3523,7 +3471,7 @@
       </x:c>
       <x:c r="C202"/>
       <x:c r="D202" t="str">
-        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_18.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_18.webp</x:v>
       </x:c>
       <x:c r="E202" t="str">
         <x:v>tak</x:v>
@@ -3539,7 +3487,7 @@
       </x:c>
       <x:c r="C203"/>
       <x:c r="D203" t="str">
-        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_19.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_19.webp</x:v>
       </x:c>
       <x:c r="E203" t="str">
         <x:v>tak</x:v>
@@ -3555,7 +3503,7 @@
       </x:c>
       <x:c r="C204"/>
       <x:c r="D204" t="str">
-        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_20.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_20.webp</x:v>
       </x:c>
       <x:c r="E204" t="str">
         <x:v>tak</x:v>
@@ -3571,7 +3519,7 @@
       </x:c>
       <x:c r="C205"/>
       <x:c r="D205" t="str">
-        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_21.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_21.webp</x:v>
       </x:c>
       <x:c r="E205" t="str">
         <x:v>tak</x:v>
@@ -3587,7 +3535,7 @@
       </x:c>
       <x:c r="C206"/>
       <x:c r="D206" t="str">
-        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_22.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwierzęta profilem/ZWPR_22.webp</x:v>
       </x:c>
       <x:c r="E206" t="str">
         <x:v>tak</x:v>
@@ -3603,7 +3551,7 @@
       </x:c>
       <x:c r="C207"/>
       <x:c r="D207" t="str">
-        <x:v>zdjecia-produktow/torby/Zwierzęta żółte tło/ZWZ_01.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwierzęta żółte tło/ZWZ_01.webp</x:v>
       </x:c>
       <x:c r="E207" t="str">
         <x:v>tak</x:v>
@@ -3619,7 +3567,7 @@
       </x:c>
       <x:c r="C208"/>
       <x:c r="D208" t="str">
-        <x:v>zdjecia-produktow/torby/Zwierzęta żółte tło/ZWZ_02.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwierzęta żółte tło/ZWZ_02.webp</x:v>
       </x:c>
       <x:c r="E208" t="str">
         <x:v>tak</x:v>
@@ -3635,7 +3583,7 @@
       </x:c>
       <x:c r="C209"/>
       <x:c r="D209" t="str">
-        <x:v>zdjecia-produktow/torby/Zwierzęta żółte tło/ZWZ_03.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwierzęta żółte tło/ZWZ_03.webp</x:v>
       </x:c>
       <x:c r="E209" t="str">
         <x:v>tak</x:v>
@@ -3651,7 +3599,7 @@
       </x:c>
       <x:c r="C210"/>
       <x:c r="D210" t="str">
-        <x:v>zdjecia-produktow/torby/Zwierzęta żółte tło/ZWZ_04.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwierzęta żółte tło/ZWZ_04.webp</x:v>
       </x:c>
       <x:c r="E210" t="str">
         <x:v>tak</x:v>
@@ -3667,7 +3615,7 @@
       </x:c>
       <x:c r="C211"/>
       <x:c r="D211" t="str">
-        <x:v>zdjecia-produktow/torby/Zwierzęta żółte tło/ZWZ_05.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwierzęta żółte tło/ZWZ_05.webp</x:v>
       </x:c>
       <x:c r="E211" t="str">
         <x:v>tak</x:v>
@@ -3683,7 +3631,7 @@
       </x:c>
       <x:c r="C212"/>
       <x:c r="D212" t="str">
-        <x:v>zdjecia-produktow/torby/Zwierzęta żółte tło/ZWZ_06.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwierzęta żółte tło/ZWZ_06.webp</x:v>
       </x:c>
       <x:c r="E212" t="str">
         <x:v>tak</x:v>
@@ -3699,7 +3647,7 @@
       </x:c>
       <x:c r="C213"/>
       <x:c r="D213" t="str">
-        <x:v>zdjecia-produktow/torby/Zwierzęta żółte tło/ZWZ_07.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwierzęta żółte tło/ZWZ_07.webp</x:v>
       </x:c>
       <x:c r="E213" t="str">
         <x:v>tak</x:v>
@@ -3715,7 +3663,7 @@
       </x:c>
       <x:c r="C214"/>
       <x:c r="D214" t="str">
-        <x:v>zdjecia-produktow/torby/Zwierzęta żółte tło/ZWZ_08.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwierzęta żółte tło/ZWZ_08.webp</x:v>
       </x:c>
       <x:c r="E214" t="str">
         <x:v>tak</x:v>
@@ -3731,7 +3679,7 @@
       </x:c>
       <x:c r="C215"/>
       <x:c r="D215" t="str">
-        <x:v>zdjecia-produktow/torby/Zwierzęta żółte tło/ZWZ_09.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwierzęta żółte tło/ZWZ_09.webp</x:v>
       </x:c>
       <x:c r="E215" t="str">
         <x:v>tak</x:v>
@@ -3747,7 +3695,7 @@
       </x:c>
       <x:c r="C216"/>
       <x:c r="D216" t="str">
-        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_01.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_01.webp</x:v>
       </x:c>
       <x:c r="E216" t="str">
         <x:v>tak</x:v>
@@ -3763,7 +3711,7 @@
       </x:c>
       <x:c r="C217"/>
       <x:c r="D217" t="str">
-        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_02.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_02.webp</x:v>
       </x:c>
       <x:c r="E217" t="str">
         <x:v>tak</x:v>
@@ -3779,7 +3727,7 @@
       </x:c>
       <x:c r="C218"/>
       <x:c r="D218" t="str">
-        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_03.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_03.webp</x:v>
       </x:c>
       <x:c r="E218" t="str">
         <x:v>tak</x:v>
@@ -3795,7 +3743,7 @@
       </x:c>
       <x:c r="C219"/>
       <x:c r="D219" t="str">
-        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_04.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_04.webp</x:v>
       </x:c>
       <x:c r="E219" t="str">
         <x:v>tak</x:v>
@@ -3811,7 +3759,7 @@
       </x:c>
       <x:c r="C220"/>
       <x:c r="D220" t="str">
-        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_05.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_05.webp</x:v>
       </x:c>
       <x:c r="E220" t="str">
         <x:v>tak</x:v>
@@ -3827,7 +3775,7 @@
       </x:c>
       <x:c r="C221"/>
       <x:c r="D221" t="str">
-        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_06.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_06.webp</x:v>
       </x:c>
       <x:c r="E221" t="str">
         <x:v>tak</x:v>
@@ -3843,7 +3791,7 @@
       </x:c>
       <x:c r="C222"/>
       <x:c r="D222" t="str">
-        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_07.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_07.webp</x:v>
       </x:c>
       <x:c r="E222" t="str">
         <x:v>tak</x:v>
@@ -3859,7 +3807,7 @@
       </x:c>
       <x:c r="C223"/>
       <x:c r="D223" t="str">
-        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_08.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_08.webp</x:v>
       </x:c>
       <x:c r="E223" t="str">
         <x:v>tak</x:v>
@@ -3875,7 +3823,7 @@
       </x:c>
       <x:c r="C224"/>
       <x:c r="D224" t="str">
-        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_09.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_09.webp</x:v>
       </x:c>
       <x:c r="E224" t="str">
         <x:v>tak</x:v>
@@ -3891,7 +3839,7 @@
       </x:c>
       <x:c r="C225"/>
       <x:c r="D225" t="str">
-        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_10.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_10.webp</x:v>
       </x:c>
       <x:c r="E225" t="str">
         <x:v>tak</x:v>
@@ -3907,7 +3855,7 @@
       </x:c>
       <x:c r="C226"/>
       <x:c r="D226" t="str">
-        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_11.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_11.webp</x:v>
       </x:c>
       <x:c r="E226" t="str">
         <x:v>tak</x:v>
@@ -3923,7 +3871,7 @@
       </x:c>
       <x:c r="C227"/>
       <x:c r="D227" t="str">
-        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_12.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_12.webp</x:v>
       </x:c>
       <x:c r="E227" t="str">
         <x:v>tak</x:v>
@@ -3939,7 +3887,7 @@
       </x:c>
       <x:c r="C228"/>
       <x:c r="D228" t="str">
-        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_13.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_13.webp</x:v>
       </x:c>
       <x:c r="E228" t="str">
         <x:v>tak</x:v>
@@ -3955,7 +3903,7 @@
       </x:c>
       <x:c r="C229"/>
       <x:c r="D229" t="str">
-        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_14.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_14.webp</x:v>
       </x:c>
       <x:c r="E229" t="str">
         <x:v>tak</x:v>
@@ -3971,7 +3919,7 @@
       </x:c>
       <x:c r="C230"/>
       <x:c r="D230" t="str">
-        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_15.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_15.webp</x:v>
       </x:c>
       <x:c r="E230" t="str">
         <x:v>tak</x:v>
@@ -3987,7 +3935,7 @@
       </x:c>
       <x:c r="C231"/>
       <x:c r="D231" t="str">
-        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_16.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_16.webp</x:v>
       </x:c>
       <x:c r="E231" t="str">
         <x:v>tak</x:v>
@@ -4003,7 +3951,7 @@
       </x:c>
       <x:c r="C232"/>
       <x:c r="D232" t="str">
-        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_17.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_17.webp</x:v>
       </x:c>
       <x:c r="E232" t="str">
         <x:v>tak</x:v>
@@ -4019,7 +3967,7 @@
       </x:c>
       <x:c r="C233"/>
       <x:c r="D233" t="str">
-        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_18.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_18.webp</x:v>
       </x:c>
       <x:c r="E233" t="str">
         <x:v>tak</x:v>
@@ -4035,7 +3983,7 @@
       </x:c>
       <x:c r="C234"/>
       <x:c r="D234" t="str">
-        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_19.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_19.webp</x:v>
       </x:c>
       <x:c r="E234" t="str">
         <x:v>tak</x:v>
@@ -4051,7 +3999,7 @@
       </x:c>
       <x:c r="C235"/>
       <x:c r="D235" t="str">
-        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_20.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_20.webp</x:v>
       </x:c>
       <x:c r="E235" t="str">
         <x:v>tak</x:v>
@@ -4067,7 +4015,7 @@
       </x:c>
       <x:c r="C236"/>
       <x:c r="D236" t="str">
-        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_21.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_21.webp</x:v>
       </x:c>
       <x:c r="E236" t="str">
         <x:v>tak</x:v>
@@ -4083,7 +4031,7 @@
       </x:c>
       <x:c r="C237"/>
       <x:c r="D237" t="str">
-        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_22.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_22.webp</x:v>
       </x:c>
       <x:c r="E237" t="str">
         <x:v>tak</x:v>
@@ -4099,7 +4047,7 @@
       </x:c>
       <x:c r="C238"/>
       <x:c r="D238" t="str">
-        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_23.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_23.webp</x:v>
       </x:c>
       <x:c r="E238" t="str">
         <x:v>tak</x:v>
@@ -4115,7 +4063,7 @@
       </x:c>
       <x:c r="C239"/>
       <x:c r="D239" t="str">
-        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_24.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_24.webp</x:v>
       </x:c>
       <x:c r="E239" t="str">
         <x:v>tak</x:v>
@@ -4131,7 +4079,7 @@
       </x:c>
       <x:c r="C240"/>
       <x:c r="D240" t="str">
-        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_25.png</x:v>
+        <x:v>zdjecia-produktow/torby/Zwięrzęta Afryki/AF_25.webp</x:v>
       </x:c>
       <x:c r="E240" t="str">
         <x:v>tak</x:v>
@@ -5677,7 +5625,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R521f9f714bc04261"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea2e869a03bb47b4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5690,72 +5638,77 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22.799999237060547">
-      <x:c r="A1" s="2" t="s">
-        <x:v>6</x:v>
-      </x:c>
+      <x:c r="A1" s="2" t="str">
+        <x:v>Jak aktualizować produkty</x:v>
+      </x:c>
+      <x:c r="B1"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="3" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B3" t="s">
-        <x:v>7</x:v>
+      <x:c r="A3" s="3" t="str">
+        <x:v>kategoria</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>Box, Breloki, Frotki, Kosmetyczka, Torby albo Workoplecak.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="3" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B4" t="s">
-        <x:v>8</x:v>
+      <x:c r="A4" s="3" t="str">
+        <x:v>seria</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>Wpisuj tylko dla kategorii Torby. Pozostałe kategorie zostaw puste.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="3" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B5" t="s">
-        <x:v>9</x:v>
+      <x:c r="A5" s="3" t="str">
+        <x:v>tytuł</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>Podpis pod zdjęciem. Może być pusty, wtedy strona zrobi podpis z nazwy pliku.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B6" t="s">
-        <x:v>10</x:v>
+      <x:c r="A6" s="3" t="str">
+        <x:v>zdjęcie</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>Ścieżka do pliku, np. zdjecia-produktow/workoplecaki/111.webp.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="3" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B7" t="s">
-        <x:v>11</x:v>
+      <x:c r="A7" s="3" t="str">
+        <x:v>aktywne</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>tak = pokazuj produkt, nie = ukryj produkt.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B8" t="s">
-        <x:v>12</x:v>
+      <x:c r="A8" s="3" t="str">
+        <x:v>notatka</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>Pole tylko dla Ciebie, strona go nie używa.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="3" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B9" t="s">
-        <x:v>14</x:v>
+      <x:c r="A9" s="3" t="str">
+        <x:v>Po zmianach</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>Zapisz arkusz jako produkty.csv i uruchom aktualizuj-produkty.bat.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="3" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B10" t="s">
-        <x:v>16</x:v>
+      <x:c r="A10" s="3" t="str">
+        <x:v>Publikacja</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>W GitHub Desktop zrób Commit, potem Push origin.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
